--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), il reste environ 7 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +41 €/mois.</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>495</v>
+        <v>550</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>ce bien est 43 % SOUS la médiane locale</t>
+          <t>ce bien est 48 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>65/100</t>
+          <t>70/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>70/100</t>
+          <t>68/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-38472aa0.xlsx
+++ b/docs/dossiers/dossier-puteaux-38472aa0.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
